--- a/data/trans_dic/P13_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,75</t>
+          <t>0,95; 3,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,17</t>
+          <t>1,3; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,28</t>
+          <t>1,4; 4,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,95</t>
+          <t>0,86; 3,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,1</t>
+          <t>0,65; 3,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,46</t>
+          <t>1,47; 3,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,66</t>
+          <t>1,42; 3,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,74</t>
+          <t>0,38; 1,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,35</t>
+          <t>0,02; 1,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,38</t>
+          <t>0,54; 2,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,75</t>
+          <t>1,37; 3,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,35</t>
+          <t>0,97; 3,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,13</t>
+          <t>2,03; 7,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,95</t>
+          <t>1,36; 3,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,94</t>
+          <t>2,64; 5,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,09</t>
+          <t>0,84; 3,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,0</t>
+          <t>1,47; 5,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,71</t>
+          <t>1,13; 2,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,21</t>
+          <t>2,16; 4,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,61</t>
+          <t>1,1; 2,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,97</t>
+          <t>2,17; 5,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,05</t>
+          <t>2,57; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,83</t>
+          <t>2,76; 5,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,15</t>
+          <t>2,18; 5,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,63</t>
+          <t>2,15; 5,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,74</t>
+          <t>2,0; 4,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,78</t>
+          <t>4,99; 8,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,32</t>
+          <t>1,78; 4,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,39</t>
+          <t>1,94; 4,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,7</t>
+          <t>2,67; 4,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,75</t>
+          <t>4,29; 6,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,16</t>
+          <t>2,24; 4,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,41</t>
+          <t>2,39; 4,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,88</t>
+          <t>0,67; 2,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,34</t>
+          <t>2,79; 6,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,12</t>
+          <t>2,62; 5,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,35</t>
+          <t>1,24; 5,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,05</t>
+          <t>2,53; 6,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,98</t>
+          <t>6,57; 11,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,72</t>
+          <t>4,6; 8,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,93</t>
+          <t>3,45; 6,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,96</t>
+          <t>1,84; 3,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,91</t>
+          <t>4,91; 7,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,61</t>
+          <t>4,12; 6,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,12</t>
+          <t>2,15; 5,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,7</t>
+          <t>1,88; 5,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,48</t>
+          <t>2,38; 6,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,59</t>
+          <t>2,4; 6,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,73</t>
+          <t>4,86; 8,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,92</t>
+          <t>3,31; 8,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,88</t>
+          <t>7,26; 13,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,41</t>
+          <t>5,09; 9,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,85</t>
+          <t>6,68; 10,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,01</t>
+          <t>2,99; 5,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,81</t>
+          <t>5,25; 8,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,42</t>
+          <t>4,26; 7,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,66</t>
+          <t>6,18; 8,73</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,37</t>
+          <t>3,81; 10,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,29</t>
+          <t>5,56; 12,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,51</t>
+          <t>2,27; 6,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,23</t>
+          <t>5,12; 9,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 12,05</t>
+          <t>6,03; 11,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,12</t>
+          <t>12,62; 20,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,25</t>
+          <t>3,99; 8,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,05</t>
+          <t>2,37; 9,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,69</t>
+          <t>5,52; 9,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,34</t>
+          <t>10,02; 15,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,99</t>
+          <t>3,64; 7,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,26</t>
+          <t>3,07; 8,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 15,13</t>
+          <t>6,51; 14,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,1</t>
+          <t>9,6; 18,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 13,01</t>
+          <t>6,09; 13,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 17,5</t>
+          <t>10,77; 17,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,23</t>
+          <t>9,22; 17,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,09; 30,62</t>
+          <t>20,86; 30,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,65; 19,98</t>
+          <t>11,47; 19,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,4; 28,47</t>
+          <t>21,99; 28,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 14,68</t>
+          <t>9,23; 15,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,74; 24,25</t>
+          <t>17,29; 24,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,27; 15,79</t>
+          <t>10,08; 15,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,4; 22,91</t>
+          <t>18,39; 22,62</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,83</t>
+          <t>2,63; 3,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,5</t>
+          <t>3,92; 5,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,13</t>
+          <t>2,84; 4,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,67</t>
+          <t>3,76; 5,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,61</t>
+          <t>4,17; 5,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,4</t>
+          <t>8,35; 10,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,33</t>
+          <t>4,8; 6,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,68</t>
+          <t>5,57; 7,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,56</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,68</t>
+          <t>6,42; 7,66</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,1</t>
+          <t>4,03; 5,1</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,46</t>
+          <t>5,08; 6,46</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4589; 18537</t>
+          <t>4716; 18125</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5844; 18925</t>
+          <t>5888; 19957</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5207</t>
+          <t>0; 3775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 9127</t>
+          <t>0; 8856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6594; 20013</t>
+          <t>6528; 20034</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3885; 17013</t>
+          <t>3691; 16465</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2077; 12270</t>
+          <t>2579; 12550</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6011</t>
+          <t>0; 6500</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13957; 33270</t>
+          <t>14109; 33607</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12895; 32367</t>
+          <t>12600; 30456</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2983; 14188</t>
+          <t>3062; 13124</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>169; 9599</t>
+          <t>167; 10098</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4060; 17506</t>
+          <t>3957; 15965</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8917; 25747</t>
+          <t>9386; 25713</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6003; 19774</t>
+          <t>5723; 17993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8710; 30182</t>
+          <t>8583; 29750</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8298; 24691</t>
+          <t>8516; 24154</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15573; 36215</t>
+          <t>16085; 35543</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4628; 17379</t>
+          <t>4706; 17523</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7376; 25580</t>
+          <t>7521; 25562</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15882; 36881</t>
+          <t>15351; 35590</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30243; 54561</t>
+          <t>28013; 54689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12836; 30082</t>
+          <t>12703; 29687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20390; 46497</t>
+          <t>20318; 49055</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17045; 38614</t>
+          <t>16422; 38509</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19234; 39678</t>
+          <t>18777; 39664</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13969; 34440</t>
+          <t>14580; 37181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12238; 30185</t>
+          <t>11555; 29401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14457; 32707</t>
+          <t>13778; 33017</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34115; 62352</t>
+          <t>35397; 62699</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11078; 28479</t>
+          <t>11731; 28874</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10560; 23764</t>
+          <t>10526; 23716</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34847; 62450</t>
+          <t>35471; 64384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58970; 93862</t>
+          <t>59657; 95299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29380; 55217</t>
+          <t>29776; 56783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24887; 47518</t>
+          <t>25753; 47039</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3199; 14946</t>
+          <t>3477; 14660</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17080; 38938</t>
+          <t>17128; 38972</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17209; 39565</t>
+          <t>16918; 38164</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10185; 47465</t>
+          <t>11034; 45775</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13039; 31199</t>
+          <t>13022; 32175</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38626; 67640</t>
+          <t>40496; 68573</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30877; 56506</t>
+          <t>29841; 54997</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23729; 42218</t>
+          <t>24583; 43683</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19600; 40926</t>
+          <t>19047; 40593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61248; 97347</t>
+          <t>60487; 97861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51998; 85543</t>
+          <t>53362; 86440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37346; 81900</t>
+          <t>34393; 80731</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7163; 22032</t>
+          <t>7269; 22013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10616; 27764</t>
+          <t>10208; 27383</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12359; 31502</t>
+          <t>11471; 30305</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26268; 48883</t>
+          <t>27229; 49120</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13711; 32014</t>
+          <t>13369; 32435</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31942; 57656</t>
+          <t>32523; 59571</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26530; 51741</t>
+          <t>25307; 49220</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35517; 53923</t>
+          <t>36566; 55513</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24513; 47543</t>
+          <t>23606; 46947</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46285; 77209</t>
+          <t>46038; 77047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42131; 72331</t>
+          <t>41527; 72714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66844; 95955</t>
+          <t>68440; 96730</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10936; 27423</t>
+          <t>11139; 30419</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17298; 38081</t>
+          <t>17214; 37825</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7002; 21767</t>
+          <t>7576; 23148</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18972; 33847</t>
+          <t>18775; 34792</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21104; 41340</t>
+          <t>20683; 40846</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43177; 71215</t>
+          <t>44677; 72460</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15171; 34943</t>
+          <t>15080; 33164</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14519; 55081</t>
+          <t>14426; 55124</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36066; 61606</t>
+          <t>35064; 60022</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66397; 101848</t>
+          <t>66519; 100636</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24953; 49744</t>
+          <t>25942; 50798</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27875; 80513</t>
+          <t>29896; 81093</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13873; 31764</t>
+          <t>13670; 31020</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24064; 47544</t>
+          <t>23894; 46925</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15891; 33424</t>
+          <t>15641; 33989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30220; 49487</t>
+          <t>30461; 49128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31404; 57536</t>
+          <t>30781; 56799</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81809; 118773</t>
+          <t>80929; 116505</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46453; 79710</t>
+          <t>45758; 77621</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>94933; 120648</t>
+          <t>93195; 119333</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49254; 79851</t>
+          <t>50210; 82355</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112948; 154430</t>
+          <t>110066; 153707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67328; 103561</t>
+          <t>66143; 103990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>129996; 161884</t>
+          <t>129949; 159794</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>85961; 125506</t>
+          <t>86111; 127563</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>135106; 188271</t>
+          <t>134333; 185836</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97926; 140090</t>
+          <t>96531; 140779</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>124843; 196052</t>
+          <t>130009; 196862</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>137011; 189635</t>
+          <t>140887; 192328</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>296176; 369679</t>
+          <t>297009; 369396</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>167866; 223954</t>
+          <t>170000; 226190</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>202910; 280723</t>
+          <t>203776; 280250</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>238296; 303755</t>
+          <t>237495; 301003</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>444062; 535778</t>
+          <t>448149; 534402</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>280753; 353544</t>
+          <t>279351; 353703</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>365723; 459618</t>
+          <t>361230; 459412</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,67</t>
+          <t>0,93; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,39</t>
+          <t>1,22; 4,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,29</t>
+          <t>1,4; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,83</t>
+          <t>0,72; 3,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,17</t>
+          <t>0,53; 3,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,5</t>
+          <t>1,37; 3,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,44</t>
+          <t>1,45; 3,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,61</t>
+          <t>0,37; 1,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,42</t>
+          <t>0,17; 2,46</t>
         </is>
       </c>
     </row>
@@ -804,19 +804,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,17</t>
+          <t>0,63; 2,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,74</t>
+          <t>1,35; 3,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,05</t>
+          <t>0,96; 3,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,02</t>
+          <t>2,55; 7,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,86</t>
+          <t>1,38; 4,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,83</t>
+          <t>2,61; 5,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,11</t>
+          <t>0,8; 2,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,0</t>
+          <t>1,91; 5,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,62</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,22</t>
+          <t>2,23; 4,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,57</t>
+          <t>1,05; 2,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,25</t>
+          <t>2,56; 5,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,03</t>
+          <t>2,64; 6,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,83</t>
+          <t>2,8; 6,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,56</t>
+          <t>2,22; 5,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,48</t>
+          <t>1,85; 4,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,79</t>
+          <t>1,99; 4,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,83</t>
+          <t>4,76; 8,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,38</t>
+          <t>1,75; 4,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,38</t>
+          <t>1,91; 4,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,85</t>
+          <t>2,57; 4,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,85</t>
+          <t>4,29; 6,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,28</t>
+          <t>2,18; 4,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,36</t>
+          <t>2,15; 3,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,82</t>
+          <t>0,57; 2,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,34</t>
+          <t>2,72; 6,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,91</t>
+          <t>2,67; 5,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,16</t>
+          <t>2,87; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,24</t>
+          <t>2,53; 6,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 11,13</t>
+          <t>6,17; 10,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,49</t>
+          <t>4,62; 8,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,14</t>
+          <t>3,75; 6,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,92</t>
+          <t>1,79; 3,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,95</t>
+          <t>4,95; 7,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,68</t>
+          <t>3,97; 6,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,05</t>
+          <t>3,67; 5,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,69</t>
+          <t>1,78; 5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,39</t>
+          <t>2,48; 6,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,34</t>
+          <t>2,5; 6,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,77</t>
+          <t>4,75; 8,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,03</t>
+          <t>3,41; 7,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,3</t>
+          <t>7,27; 13,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,91</t>
+          <t>5,37; 10,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,14</t>
+          <t>6,67; 10,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,94</t>
+          <t>3,04; 5,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,79</t>
+          <t>5,37; 8,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,46</t>
+          <t>4,31; 7,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,73</t>
+          <t>6,12; 8,75</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,4</t>
+          <t>3,88; 9,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,21</t>
+          <t>5,21; 11,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,92</t>
+          <t>2,31; 6,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,49</t>
+          <t>4,99; 9,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,91</t>
+          <t>5,83; 11,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 20,47</t>
+          <t>12,45; 20,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,78</t>
+          <t>3,8; 8,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,06</t>
+          <t>7,12; 11,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,44</t>
+          <t>5,81; 9,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,16</t>
+          <t>10,21; 15,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,13</t>
+          <t>3,68; 7,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,32</t>
+          <t>6,58; 9,51</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,78</t>
+          <t>6,0; 14,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 18,85</t>
+          <t>9,42; 18,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,23</t>
+          <t>5,97; 12,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,77; 17,37</t>
+          <t>10,79; 17,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,01</t>
+          <t>9,58; 17,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,86; 30,04</t>
+          <t>20,84; 30,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,47; 19,46</t>
+          <t>11,21; 19,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,99; 28,16</t>
+          <t>22,03; 28,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,14</t>
+          <t>8,95; 14,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,29; 24,14</t>
+          <t>17,48; 24,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,85</t>
+          <t>10,16; 15,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,39; 22,62</t>
+          <t>18,28; 22,59</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,89</t>
+          <t>2,59; 3,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,43</t>
+          <t>3,96; 5,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,15</t>
+          <t>2,85; 4,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,7</t>
+          <t>4,55; 6,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,69</t>
+          <t>4,15; 5,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 10,39</t>
+          <t>8,41; 10,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,39</t>
+          <t>4,77; 6,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,66</t>
+          <t>6,79; 8,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,52</t>
+          <t>3,54; 4,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,66</t>
+          <t>6,35; 7,7</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,1</t>
+          <t>4,05; 5,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,46</t>
+          <t>5,9; 6,91</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>6166</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4716; 18125</t>
+          <t>4604; 19062</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5888; 19957</t>
+          <t>5543; 19104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3775</t>
+          <t>0; 5259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8856</t>
+          <t>0; 17093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6528; 20034</t>
+          <t>6558; 19662</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3691; 16465</t>
+          <t>3086; 16059</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2579; 12550</t>
+          <t>2087; 12353</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6500</t>
+          <t>0; 8107</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14109; 33607</t>
+          <t>13193; 31935</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12600; 30456</t>
+          <t>12826; 30680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3062; 13124</t>
+          <t>2993; 14284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>167; 10098</t>
+          <t>1314; 18976</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>37543</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3957; 15965</t>
+          <t>4601; 17826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9386; 25713</t>
+          <t>9262; 26700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5723; 17993</t>
+          <t>5693; 18368</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8583; 29750</t>
+          <t>12152; 35673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8516; 24154</t>
+          <t>8658; 25267</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16085; 35543</t>
+          <t>15908; 35907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4706; 17523</t>
+          <t>4492; 15792</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7521; 25562</t>
+          <t>9571; 27339</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15351; 35590</t>
+          <t>15651; 36994</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28013; 54689</t>
+          <t>28917; 54832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12703; 29687</t>
+          <t>12138; 29259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20318; 49055</t>
+          <t>25012; 53789</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34844</t>
+          <t>37438</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16422; 38509</t>
+          <t>16884; 38467</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18777; 39664</t>
+          <t>19081; 41153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14580; 37181</t>
+          <t>14862; 34560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11555; 29401</t>
+          <t>11494; 29282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13778; 33017</t>
+          <t>13700; 34081</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35397; 62699</t>
+          <t>33762; 62429</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11731; 28874</t>
+          <t>11546; 29154</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10526; 23716</t>
+          <t>11892; 25930</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35471; 64384</t>
+          <t>34176; 64056</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59657; 95299</t>
+          <t>59634; 94225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29776; 56783</t>
+          <t>29001; 56955</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25753; 47039</t>
+          <t>26715; 49074</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33101</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>66819</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3477; 14660</t>
+          <t>2952; 15402</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17128; 38972</t>
+          <t>16720; 38511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16918; 38164</t>
+          <t>17253; 37863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11034; 45775</t>
+          <t>20103; 43027</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13022; 32175</t>
+          <t>13056; 31642</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40496; 68573</t>
+          <t>38003; 67213</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29841; 54997</t>
+          <t>29945; 56441</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24583; 43683</t>
+          <t>27599; 46823</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19047; 40593</t>
+          <t>18490; 40779</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60487; 97861</t>
+          <t>60926; 97898</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53362; 86440</t>
+          <t>51321; 86189</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34393; 80731</t>
+          <t>52610; 86034</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36787</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>50711</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81360</t>
+          <t>89408</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7269; 22013</t>
+          <t>6889; 20826</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10208; 27383</t>
+          <t>10638; 26933</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11471; 30305</t>
+          <t>11925; 31196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27229; 49120</t>
+          <t>28917; 52471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13369; 32435</t>
+          <t>13771; 31725</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32523; 59571</t>
+          <t>32551; 59875</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25307; 49220</t>
+          <t>26687; 50029</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36566; 55513</t>
+          <t>40590; 61840</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23606; 46947</t>
+          <t>24049; 47397</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46038; 77047</t>
+          <t>47009; 76901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41527; 72714</t>
+          <t>42060; 72553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68440; 96730</t>
+          <t>74393; 106433</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59747</t>
+          <t>67429</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11139; 30419</t>
+          <t>11347; 27202</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17214; 37825</t>
+          <t>16136; 36530</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7576; 23148</t>
+          <t>7724; 23034</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18775; 34792</t>
+          <t>20235; 37021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20683; 40846</t>
+          <t>19978; 39466</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44677; 72460</t>
+          <t>44071; 72862</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15080; 33164</t>
+          <t>14371; 33643</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14426; 55124</t>
+          <t>31278; 48341</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35064; 60022</t>
+          <t>36920; 62870</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66519; 100636</t>
+          <t>67759; 102294</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25942; 50798</t>
+          <t>26198; 51089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29896; 81093</t>
+          <t>55564; 80318</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106627</t>
+          <t>116063</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>145865</t>
+          <t>157798</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13670; 31020</t>
+          <t>12593; 30587</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23894; 46925</t>
+          <t>23441; 46635</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15641; 33989</t>
+          <t>15354; 32929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30461; 49128</t>
+          <t>33463; 53105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30781; 56799</t>
+          <t>31974; 57152</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80929; 116505</t>
+          <t>80818; 118797</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45758; 77621</t>
+          <t>44719; 77974</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>93195; 119333</t>
+          <t>101884; 129696</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50210; 82355</t>
+          <t>48681; 81259</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110066; 153707</t>
+          <t>111320; 155400</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66143; 103990</t>
+          <t>66640; 102968</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>129949; 159794</t>
+          <t>141272; 174569</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>278150</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>462601</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>86111; 127563</t>
+          <t>84933; 127475</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134333; 185836</t>
+          <t>135453; 190759</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>96531; 140779</t>
+          <t>96776; 141560</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>130009; 196862</t>
+          <t>160618; 213718</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>140887; 192328</t>
+          <t>140324; 190043</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>297009; 369396</t>
+          <t>299047; 365052</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>170000; 226190</t>
+          <t>168680; 224144</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>203776; 280250</t>
+          <t>253214; 305625</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>237495; 301003</t>
+          <t>235509; 302413</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>448149; 534402</t>
+          <t>443214; 537191</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>279351; 353703</t>
+          <t>281018; 352040</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>361230; 459412</t>
+          <t>427953; 501471</t>
         </is>
       </c>
     </row>
